--- a/multi seed generators/second batch/classification/results/aggregated/compute_mean_sd.xlsx
+++ b/multi seed generators/second batch/classification/results/aggregated/compute_mean_sd.xlsx
@@ -249,12 +249,10 @@
       <c r="H3" t="n">
         <v>0.0</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I3"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -449,12 +447,10 @@
       <c r="H7" t="n">
         <v>0.0</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I7"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -649,12 +645,10 @@
       <c r="H11" t="n">
         <v>0.0</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I11"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -849,12 +843,10 @@
       <c r="H15" t="n">
         <v>0.0</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I15"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1049,12 +1041,10 @@
       <c r="H19" t="n">
         <v>0.0</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I19"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1249,12 +1239,10 @@
       <c r="H23" t="n">
         <v>0.0</v>
       </c>
-      <c r="I23" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I23"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1449,12 +1437,10 @@
       <c r="H27" t="n">
         <v>0.0</v>
       </c>
-      <c r="I27" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I27"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1649,12 +1635,10 @@
       <c r="H31" t="n">
         <v>0.0</v>
       </c>
-      <c r="I31" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I31"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -1849,12 +1833,10 @@
       <c r="H35" t="n">
         <v>0.0</v>
       </c>
-      <c r="I35" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I35"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2049,12 +2031,10 @@
       <c r="H39" t="n">
         <v>0.0</v>
       </c>
-      <c r="I39" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I39"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2249,12 +2229,10 @@
       <c r="H43" t="n">
         <v>0.0</v>
       </c>
-      <c r="I43" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I43"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -2449,12 +2427,10 @@
       <c r="H47" t="n">
         <v>0.0</v>
       </c>
-      <c r="I47" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I47"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -2649,12 +2625,10 @@
       <c r="H51" t="n">
         <v>0.0</v>
       </c>
-      <c r="I51" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I51"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -2849,12 +2823,10 @@
       <c r="H55" t="n">
         <v>0.0</v>
       </c>
-      <c r="I55" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I55"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -3049,12 +3021,10 @@
       <c r="H59" t="n">
         <v>0.0</v>
       </c>
-      <c r="I59" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I59"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -3249,12 +3219,10 @@
       <c r="H63" t="n">
         <v>0.0</v>
       </c>
-      <c r="I63" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I63"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -3449,12 +3417,10 @@
       <c r="H67" t="n">
         <v>0.0</v>
       </c>
-      <c r="I67" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I67"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -3649,12 +3615,10 @@
       <c r="H71" t="n">
         <v>0.0</v>
       </c>
-      <c r="I71" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I71"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -3849,12 +3813,10 @@
       <c r="H75" t="n">
         <v>0.0</v>
       </c>
-      <c r="I75" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I75"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -4049,12 +4011,10 @@
       <c r="H79" t="n">
         <v>0.0</v>
       </c>
-      <c r="I79" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I79"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -4249,12 +4209,10 @@
       <c r="H83" t="n">
         <v>0.0</v>
       </c>
-      <c r="I83" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I83"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -4449,12 +4407,10 @@
       <c r="H87" t="n">
         <v>0.0</v>
       </c>
-      <c r="I87" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I87"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -4649,12 +4605,10 @@
       <c r="H91" t="n">
         <v>0.0</v>
       </c>
-      <c r="I91" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I91"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -4849,12 +4803,10 @@
       <c r="H95" t="n">
         <v>0.0</v>
       </c>
-      <c r="I95" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I95"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -5049,12 +5001,10 @@
       <c r="H99" t="n">
         <v>0.0</v>
       </c>
-      <c r="I99" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I99"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -5249,12 +5199,10 @@
       <c r="H103" t="n">
         <v>0.0</v>
       </c>
-      <c r="I103" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I103"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -5449,12 +5397,10 @@
       <c r="H107" t="n">
         <v>0.0</v>
       </c>
-      <c r="I107" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I107"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -5649,12 +5595,10 @@
       <c r="H111" t="n">
         <v>0.0</v>
       </c>
-      <c r="I111" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I111"/>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -5849,12 +5793,10 @@
       <c r="H115" t="n">
         <v>0.0</v>
       </c>
-      <c r="I115" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I115"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -6049,12 +5991,10 @@
       <c r="H119" t="n">
         <v>0.0</v>
       </c>
-      <c r="I119" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I119"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -6249,12 +6189,10 @@
       <c r="H123" t="n">
         <v>0.0</v>
       </c>
-      <c r="I123" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I123"/>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K123" t="n">
@@ -6449,12 +6387,10 @@
       <c r="H127" t="n">
         <v>0.0</v>
       </c>
-      <c r="I127" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I127"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -6649,12 +6585,10 @@
       <c r="H131" t="n">
         <v>0.0</v>
       </c>
-      <c r="I131" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I131"/>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K131" t="n">
@@ -6849,12 +6783,10 @@
       <c r="H135" t="n">
         <v>0.0</v>
       </c>
-      <c r="I135" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I135"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K135" t="n">
@@ -7049,12 +6981,10 @@
       <c r="H139" t="n">
         <v>0.0</v>
       </c>
-      <c r="I139" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I139"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K139" t="n">
@@ -7249,12 +7179,10 @@
       <c r="H143" t="n">
         <v>0.0</v>
       </c>
-      <c r="I143" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I143"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K143" t="n">
@@ -7449,12 +7377,10 @@
       <c r="H147" t="n">
         <v>0.0</v>
       </c>
-      <c r="I147" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I147"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -7649,12 +7575,10 @@
       <c r="H151" t="n">
         <v>0.0</v>
       </c>
-      <c r="I151" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I151"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K151" t="n">
@@ -7849,12 +7773,10 @@
       <c r="H155" t="n">
         <v>0.0</v>
       </c>
-      <c r="I155" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I155"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K155" t="n">
@@ -8049,12 +7971,10 @@
       <c r="H159" t="n">
         <v>0.0</v>
       </c>
-      <c r="I159" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I159"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K159" t="n">
@@ -8249,12 +8169,10 @@
       <c r="H163" t="n">
         <v>0.0</v>
       </c>
-      <c r="I163" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I163"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K163" t="n">
@@ -8449,12 +8367,10 @@
       <c r="H167" t="n">
         <v>0.0</v>
       </c>
-      <c r="I167" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I167"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -8649,12 +8565,10 @@
       <c r="H171" t="n">
         <v>0.0</v>
       </c>
-      <c r="I171" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I171"/>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K171" t="n">
@@ -8849,12 +8763,10 @@
       <c r="H175" t="n">
         <v>0.0</v>
       </c>
-      <c r="I175" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I175"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K175" t="n">
@@ -9049,12 +8961,10 @@
       <c r="H179" t="n">
         <v>0.0</v>
       </c>
-      <c r="I179" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I179"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K179" t="n">
@@ -9249,12 +9159,10 @@
       <c r="H183" t="n">
         <v>0.0</v>
       </c>
-      <c r="I183" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I183"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K183" t="n">
@@ -9449,12 +9357,10 @@
       <c r="H187" t="n">
         <v>0.0</v>
       </c>
-      <c r="I187" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I187"/>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -9649,12 +9555,10 @@
       <c r="H191" t="n">
         <v>0.0</v>
       </c>
-      <c r="I191" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I191"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K191" t="n">
@@ -9849,12 +9753,10 @@
       <c r="H195" t="n">
         <v>0.0</v>
       </c>
-      <c r="I195" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I195"/>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K195" t="n">
@@ -10049,12 +9951,10 @@
       <c r="H199" t="n">
         <v>0.0</v>
       </c>
-      <c r="I199" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I199"/>
       <c r="J199" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K199" t="n">
@@ -10249,12 +10149,10 @@
       <c r="H203" t="n">
         <v>0.0</v>
       </c>
-      <c r="I203" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I203"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K203" t="n">
@@ -10449,12 +10347,10 @@
       <c r="H207" t="n">
         <v>0.0</v>
       </c>
-      <c r="I207" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I207"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -10649,12 +10545,10 @@
       <c r="H211" t="n">
         <v>0.0</v>
       </c>
-      <c r="I211" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I211"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K211" t="n">
@@ -10849,12 +10743,10 @@
       <c r="H215" t="n">
         <v>0.0</v>
       </c>
-      <c r="I215" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I215"/>
       <c r="J215" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K215" t="n">
@@ -11049,12 +10941,10 @@
       <c r="H219" t="n">
         <v>0.0</v>
       </c>
-      <c r="I219" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I219"/>
       <c r="J219" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K219" t="n">
@@ -11249,12 +11139,10 @@
       <c r="H223" t="n">
         <v>0.0</v>
       </c>
-      <c r="I223" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I223"/>
       <c r="J223" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K223" t="n">
@@ -11449,12 +11337,10 @@
       <c r="H227" t="n">
         <v>0.0</v>
       </c>
-      <c r="I227" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I227"/>
       <c r="J227" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K227" t="n">
@@ -11649,12 +11535,10 @@
       <c r="H231" t="n">
         <v>0.0</v>
       </c>
-      <c r="I231" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I231"/>
       <c r="J231" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K231" t="n">
@@ -11849,12 +11733,10 @@
       <c r="H235" t="n">
         <v>0.0</v>
       </c>
-      <c r="I235" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I235"/>
       <c r="J235" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K235" t="n">
@@ -12049,12 +11931,10 @@
       <c r="H239" t="n">
         <v>0.0</v>
       </c>
-      <c r="I239" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I239"/>
       <c r="J239" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K239" t="n">
@@ -12249,12 +12129,10 @@
       <c r="H243" t="n">
         <v>0.0</v>
       </c>
-      <c r="I243" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I243"/>
       <c r="J243" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K243" t="n">
@@ -12449,12 +12327,10 @@
       <c r="H247" t="n">
         <v>0.0</v>
       </c>
-      <c r="I247" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I247"/>
       <c r="J247" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K247" t="n">
@@ -12649,12 +12525,10 @@
       <c r="H251" t="n">
         <v>0.0</v>
       </c>
-      <c r="I251" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I251"/>
       <c r="J251" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K251" t="n">
@@ -12849,12 +12723,10 @@
       <c r="H255" t="n">
         <v>0.0</v>
       </c>
-      <c r="I255" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I255"/>
       <c r="J255" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K255" t="n">
@@ -13049,12 +12921,10 @@
       <c r="H259" t="n">
         <v>0.0</v>
       </c>
-      <c r="I259" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I259"/>
       <c r="J259" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K259" t="n">
@@ -13249,12 +13119,10 @@
       <c r="H263" t="n">
         <v>0.0</v>
       </c>
-      <c r="I263" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I263"/>
       <c r="J263" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K263" t="n">
@@ -13449,12 +13317,10 @@
       <c r="H267" t="n">
         <v>0.0</v>
       </c>
-      <c r="I267" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I267"/>
       <c r="J267" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K267" t="n">
@@ -13649,12 +13515,10 @@
       <c r="H271" t="n">
         <v>0.0</v>
       </c>
-      <c r="I271" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I271"/>
       <c r="J271" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K271" t="n">
@@ -13849,12 +13713,10 @@
       <c r="H275" t="n">
         <v>0.0</v>
       </c>
-      <c r="I275" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I275"/>
       <c r="J275" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K275" t="n">
@@ -14049,12 +13911,10 @@
       <c r="H279" t="n">
         <v>0.0</v>
       </c>
-      <c r="I279" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I279"/>
       <c r="J279" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K279" t="n">
@@ -14249,12 +14109,10 @@
       <c r="H283" t="n">
         <v>0.0</v>
       </c>
-      <c r="I283" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I283"/>
       <c r="J283" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K283" t="n">
@@ -14449,12 +14307,10 @@
       <c r="H287" t="n">
         <v>0.0</v>
       </c>
-      <c r="I287" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I287"/>
       <c r="J287" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K287" t="n">
